--- a/Links/Part Links.xlsx
+++ b/Links/Part Links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronics Project\Armageddon\Links\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095C77E1-8651-4308-A238-0F64E7A69CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A08531-02C7-44C5-9594-666078991DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="8475" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9600" yWindow="5640" windowWidth="19360" windowHeight="10480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,13 +74,13 @@
     <t>https://uk.farnell.com/littelfuse/smaj28a/diode-tvs-28v-400w-5-uni-sma/dp/1827604</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>A768EB226M1HLAE048</t>
   </si>
   <si>
     <t>Aluminium Polymer 22uF/50V</t>
+  </si>
+  <si>
+    <t>C2</t>
   </si>
 </sst>
 </file>
@@ -462,13 +462,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
